--- a/artfynd/A 19470-2022 artfynd.xlsx
+++ b/artfynd/A 19470-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 19470-2022 artfynd.xlsx
+++ b/artfynd/A 19470-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY220"/>
+  <dimension ref="A1:AZ220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104845483</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796638</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796662</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1073,6 +1093,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796663</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1170,6 +1195,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796648</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1267,6 +1297,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796649</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1364,6 +1399,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796650</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1461,6 +1501,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796651</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1558,6 +1603,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796652</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1655,6 +1705,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796653</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1752,6 +1807,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796654</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1849,6 +1909,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796655</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1946,6 +2011,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796656</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2043,6 +2113,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796657</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2140,6 +2215,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796658</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2237,6 +2317,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796659</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2334,6 +2419,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796660</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2431,6 +2521,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796661</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2528,6 +2623,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796863</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2625,6 +2725,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796864</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2722,6 +2827,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796865</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2819,6 +2929,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796866</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2916,6 +3031,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796867</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3013,6 +3133,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796868</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3110,6 +3235,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796869</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3207,6 +3337,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796870</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3304,6 +3439,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796871</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3401,6 +3541,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796872</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3498,6 +3643,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796873</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3595,6 +3745,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796874</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3692,6 +3847,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796875</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3789,6 +3949,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796876</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3886,6 +4051,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796877</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3983,6 +4153,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796879</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4080,6 +4255,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796881</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4177,6 +4357,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796882</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4274,6 +4459,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796883</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4371,6 +4561,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796645</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4468,6 +4663,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796605</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4565,6 +4765,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796606</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4662,6 +4867,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796607</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4759,6 +4969,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796608</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4856,6 +5071,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796609</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4953,6 +5173,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796610</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5050,6 +5275,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796611</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5147,6 +5377,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796612</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5244,6 +5479,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796613</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5341,6 +5581,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796614</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5438,6 +5683,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796615</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5535,6 +5785,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796616</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5632,6 +5887,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796841</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5729,6 +5989,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796842</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5826,6 +6091,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796647</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5923,6 +6193,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104821989</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6020,6 +6295,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104821990</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6117,6 +6397,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104845480</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6214,6 +6499,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104845481</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6311,6 +6601,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796634</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6408,6 +6703,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796855</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6510,6 +6810,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796604</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6612,6 +6917,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796839</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6714,6 +7024,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796840</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6811,6 +7126,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796554</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6908,6 +7228,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796555</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7005,6 +7330,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796556</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7102,6 +7432,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796557</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7199,6 +7534,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796558</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7296,6 +7636,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796559</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7393,6 +7738,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796560</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7490,6 +7840,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796789</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7587,6 +7942,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796790</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7684,6 +8044,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796791</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7781,6 +8146,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796792</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7878,6 +8248,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796793</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7975,6 +8350,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796794</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8072,6 +8452,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796795</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8169,6 +8554,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796796</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8266,6 +8656,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796799</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8363,6 +8758,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796622</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8460,6 +8860,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796623</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8557,6 +8962,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796624</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8654,6 +9064,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796625</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8751,6 +9166,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796626</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8848,6 +9268,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796627</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8945,6 +9370,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796628</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9042,6 +9472,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796850</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9139,6 +9574,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796851</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9236,6 +9676,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796852</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9333,6 +9778,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796853</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9430,6 +9880,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796671</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9527,6 +9982,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796672</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9624,6 +10084,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796673</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9721,6 +10186,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796674</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9818,6 +10288,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796675</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9915,6 +10390,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796676</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10012,6 +10492,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796677</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10109,6 +10594,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796678</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10206,6 +10696,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796887</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10303,6 +10798,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796888</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10400,6 +10900,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796889</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10497,6 +11002,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796890</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10594,6 +11104,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796639</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10691,6 +11206,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796640</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10788,6 +11308,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796641</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10885,6 +11410,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796642</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -10982,6 +11512,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796643</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11079,6 +11614,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796644</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11176,6 +11716,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796857</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11273,6 +11818,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796858</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11370,6 +11920,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796859</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11467,6 +12022,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796860</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11564,6 +12124,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796861</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11661,6 +12226,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796838</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11758,6 +12328,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796567</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11855,6 +12430,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796568</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -11952,6 +12532,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796569</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12049,6 +12634,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796570</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12146,6 +12736,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796571</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12243,6 +12838,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796572</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12340,6 +12940,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796573</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12437,6 +13042,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796574</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12534,6 +13144,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796575</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12631,6 +13246,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796576</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12728,6 +13348,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796577</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12825,6 +13450,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796578</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -12922,6 +13552,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796579</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13019,6 +13654,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796580</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13116,6 +13756,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796581</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13213,6 +13858,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796582</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13310,6 +13960,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796583</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13407,6 +14062,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796584</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13504,6 +14164,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796585</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13601,6 +14266,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796586</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13698,6 +14368,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796587</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13795,6 +14470,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796588</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -13892,6 +14572,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796589</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -13989,6 +14674,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796590</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14086,6 +14776,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796800</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14183,6 +14878,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796801</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14280,6 +14980,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796802</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14377,6 +15082,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796803</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14474,6 +15184,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796804</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14571,6 +15286,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796805</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14668,6 +15388,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796806</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -14765,6 +15490,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796807</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -14862,6 +15592,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796808</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -14959,6 +15694,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796809</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15056,6 +15796,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796810</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15153,6 +15898,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796811</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15250,6 +16000,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796812</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15347,6 +16102,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796813</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15444,6 +16204,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796814</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15541,6 +16306,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796815</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15638,6 +16408,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796817</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -15735,6 +16510,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796819</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -15832,6 +16612,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796629</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -15929,6 +16714,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796630</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16026,6 +16816,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796631</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16123,6 +16918,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796632</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16220,6 +17020,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796633</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16317,6 +17122,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796854</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16419,6 +17229,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796836</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16516,6 +17331,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796884</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -16613,6 +17433,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796664</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -16710,6 +17535,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796665</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -16807,6 +17637,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796666</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -16904,6 +17739,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796667</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17001,6 +17841,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796668</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17098,6 +17943,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796669</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17195,6 +18045,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796670</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17292,6 +18147,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796862</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17389,6 +18249,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796885</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -17486,6 +18351,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796886</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -17588,6 +18458,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796837</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -17685,6 +18560,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796553</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -17787,6 +18667,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796834</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -17889,6 +18774,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796602</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -17991,6 +18881,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796603</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18088,6 +18983,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796646</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18185,6 +19085,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796849</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18282,6 +19187,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796617</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -18379,6 +19289,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796618</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -18476,6 +19391,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796619</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -18573,6 +19493,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796620</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -18670,6 +19595,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796621</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -18767,6 +19697,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796843</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -18864,6 +19799,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796844</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -18961,6 +19901,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796845</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19058,6 +20003,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796847</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19155,6 +20105,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796848</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19252,6 +20207,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796635</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -19349,6 +20309,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796636</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -19446,6 +20411,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796856</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -19543,6 +20513,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796591</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -19640,6 +20615,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796592</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -19737,6 +20717,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796593</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -19834,6 +20819,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796594</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -19931,6 +20921,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796595</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20028,6 +21023,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796596</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20125,6 +21125,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796597</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -20222,6 +21227,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796598</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -20319,6 +21329,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796599</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -20416,6 +21431,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796600</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -20513,6 +21533,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796601</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -20610,6 +21635,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796820</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -20707,6 +21737,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796821</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -20804,6 +21839,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796822</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -20901,6 +21941,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796823</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -20998,6 +22043,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796824</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21095,6 +22145,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796825</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21192,6 +22247,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796826</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -21289,6 +22349,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796827</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -21386,6 +22451,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796828</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -21483,6 +22553,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796829</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -21580,6 +22655,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796830</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -21677,6 +22757,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796831</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -21774,6 +22859,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796832</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -21871,6 +22961,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796833</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -21977,8 +23072,234 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104845482</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>